--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008412105359976642</v>
       </c>
       <c r="C2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>9775442</v>
+        <v>4771003</v>
       </c>
       <c r="L2" t="n">
-        <v>6229610</v>
+        <v>2977163</v>
       </c>
       <c r="M2" t="n">
-        <v>1695400</v>
+        <v>776298</v>
       </c>
       <c r="N2" t="n">
-        <v>119566</v>
+        <v>43420</v>
       </c>
       <c r="O2" t="n">
-        <v>965643</v>
+        <v>457030</v>
       </c>
       <c r="P2" t="n">
-        <v>370494</v>
+        <v>177776</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999966025352478</v>
+        <v>0.999992847442627</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9777665734291077</v>
+        <v>0.956032931804657</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9346315860748291</v>
+        <v>0.8845655918121338</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9282350540161133</v>
+        <v>0.8667600154876709</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8489130139350891</v>
+        <v>0.6729592084884644</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9476667046546936</v>
+        <v>0.8968124985694885</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9661213159561157</v>
+        <v>0.9321650862693787</v>
       </c>
       <c r="X2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="AG2" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AH2" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AI2" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567450881004333</v>
+        <v>0.9567357897758484</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112150073051453</v>
+        <v>0.9112488627433777</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582985401153564</v>
+        <v>0.8582139611244202</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627530455589294</v>
+        <v>0.6625582575798035</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020664095878601</v>
+        <v>0.9019841551780701</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -792,16 +792,16 @@
         <v>0.002017379093236049</v>
       </c>
       <c r="C3" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>9775442</v>
+        <v>4771003</v>
       </c>
       <c r="E3" t="n">
-        <v>294799</v>
+        <v>260704</v>
       </c>
       <c r="F3" t="n">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="G3" t="n">
         <v>482</v>
@@ -813,109 +813,109 @@
         <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>20032815</v>
+        <v>10016577</v>
       </c>
       <c r="K3" t="n">
-        <v>22363880</v>
+        <v>11076048</v>
       </c>
       <c r="L3" t="n">
-        <v>25708829</v>
+        <v>12681732</v>
       </c>
       <c r="M3" t="n">
-        <v>30664957</v>
+        <v>15278454</v>
       </c>
       <c r="N3" t="n">
-        <v>32459851</v>
+        <v>16219435</v>
       </c>
       <c r="O3" t="n">
-        <v>31588116</v>
+        <v>15768041</v>
       </c>
       <c r="P3" t="n">
-        <v>32259663</v>
+        <v>16123381</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9704563617706299</v>
+        <v>0.9477298855781555</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9562433958053589</v>
+        <v>0.9134214520454407</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9099565148353577</v>
+        <v>0.8331058025360107</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6714588403701782</v>
+        <v>0.4875145852565765</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9487943053245544</v>
+        <v>0.8979454636573792</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9584757089614868</v>
+        <v>0.9197752475738525</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="Z3" t="n">
-        <v>395630</v>
+        <v>197858</v>
       </c>
       <c r="AA3" t="n">
-        <v>17032</v>
+        <v>8531</v>
       </c>
       <c r="AB3" t="n">
-        <v>13547</v>
+        <v>6780</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20033244</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>22150033</v>
+        <v>11077458</v>
       </c>
       <c r="AG3" t="n">
-        <v>25566849</v>
+        <v>12781334</v>
       </c>
       <c r="AH3" t="n">
-        <v>30532165</v>
+        <v>15265735</v>
       </c>
       <c r="AI3" t="n">
-        <v>32421126</v>
+        <v>16210502</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31541812</v>
+        <v>15770758</v>
       </c>
       <c r="AK3" t="n">
-        <v>32246147</v>
+        <v>16123064</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576732516288757</v>
+        <v>0.9576404094696045</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100743532180786</v>
+        <v>0.9101204872131348</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578290939331055</v>
+        <v>0.8577921390533447</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66222083568573</v>
+        <v>0.6621193885803223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016799926757812</v>
+        <v>0.9016509652137756</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -929,13 +929,13 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>207669</v>
+        <v>204965</v>
       </c>
       <c r="E4" t="n">
-        <v>6229610</v>
+        <v>2977163</v>
       </c>
       <c r="F4" t="n">
-        <v>75120</v>
+        <v>74954</v>
       </c>
       <c r="G4" t="n">
         <v>1093</v>
@@ -947,109 +947,109 @@
         <v>55</v>
       </c>
       <c r="J4" t="n">
-        <v>429</v>
+        <v>45</v>
       </c>
       <c r="K4" t="n">
-        <v>222284</v>
+        <v>219414</v>
       </c>
       <c r="L4" t="n">
-        <v>435701</v>
+        <v>388515</v>
       </c>
       <c r="M4" t="n">
-        <v>131077</v>
+        <v>119334</v>
       </c>
       <c r="N4" t="n">
-        <v>21280</v>
+        <v>21101</v>
       </c>
       <c r="O4" t="n">
-        <v>53326</v>
+        <v>52586</v>
       </c>
       <c r="P4" t="n">
-        <v>12992</v>
+        <v>12937</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999983012676239</v>
+        <v>0.9999964237213135</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9740977883338928</v>
+        <v>0.9518632888793945</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9453139901161194</v>
+        <v>0.8987619876861572</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9190049767494202</v>
+        <v>0.8495997786521912</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7498298287391663</v>
+        <v>0.5654197931289673</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9482301473617554</v>
+        <v>0.8973786234855652</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9622833132743835</v>
+        <v>0.9259286522865295</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>407180</v>
+        <v>203532</v>
       </c>
       <c r="Z4" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AA4" t="n">
-        <v>165287</v>
+        <v>82724</v>
       </c>
       <c r="AB4" t="n">
-        <v>10949</v>
+        <v>5477</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>436131</v>
+        <v>218004</v>
       </c>
       <c r="AG4" t="n">
-        <v>577681</v>
+        <v>288913</v>
       </c>
       <c r="AH4" t="n">
-        <v>263869</v>
+        <v>132053</v>
       </c>
       <c r="AI4" t="n">
-        <v>60005</v>
+        <v>30034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99630</v>
+        <v>49869</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572089314460754</v>
+        <v>0.9571878910064697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106443524360657</v>
+        <v>0.9106842875480652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580637574195862</v>
+        <v>0.8580030798912048</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624868512153625</v>
+        <v>0.6623387336730957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018731117248535</v>
+        <v>0.9018175005912781</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
@@ -1059,16 +1059,16 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>8416</v>
+        <v>8332</v>
       </c>
       <c r="E5" t="n">
-        <v>120399</v>
+        <v>108281</v>
       </c>
       <c r="F5" t="n">
-        <v>1695400</v>
+        <v>776298</v>
       </c>
       <c r="G5" t="n">
-        <v>9578</v>
+        <v>9528</v>
       </c>
       <c r="H5" t="n">
         <v>28797</v>
@@ -1080,131 +1080,131 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>297594</v>
+        <v>263135</v>
       </c>
       <c r="L5" t="n">
-        <v>285060</v>
+        <v>282190</v>
       </c>
       <c r="M5" t="n">
-        <v>167766</v>
+        <v>155514</v>
       </c>
       <c r="N5" t="n">
-        <v>58503</v>
+        <v>45644</v>
       </c>
       <c r="O5" t="n">
-        <v>52115</v>
+        <v>51943</v>
       </c>
       <c r="P5" t="n">
-        <v>16051</v>
+        <v>15506</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999868869781494</v>
+        <v>0.9999972581863403</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9840817451477051</v>
+        <v>0.9704494476318359</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9779308438301086</v>
+        <v>0.9589270353317261</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9908496737480164</v>
+        <v>0.9831687211990356</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9975571036338806</v>
+        <v>0.9959126114845276</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9967714548110962</v>
+        <v>0.9935988187789917</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9991106986999512</v>
+        <v>0.9982581734657288</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15974</v>
+        <v>7983</v>
       </c>
       <c r="Z5" t="n">
-        <v>169599</v>
+        <v>84824</v>
       </c>
       <c r="AA5" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AB5" t="n">
-        <v>19854</v>
+        <v>9943</v>
       </c>
       <c r="AC5" t="n">
-        <v>58195</v>
+        <v>29128</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>426359</v>
+        <v>213244</v>
       </c>
       <c r="AG5" t="n">
-        <v>585836</v>
+        <v>292949</v>
       </c>
       <c r="AH5" t="n">
-        <v>264888</v>
+        <v>132511</v>
       </c>
       <c r="AI5" t="n">
-        <v>60148</v>
+        <v>30093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100066</v>
+        <v>50057</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735912084579468</v>
+        <v>0.9735910296440125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643740057945251</v>
+        <v>0.9643676280975342</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838098883628845</v>
+        <v>0.9837985038757324</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210225105286</v>
+        <v>0.9963179230690002</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938854575157166</v>
+        <v>0.9938806891441345</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983761310577393</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>6164</v>
+        <v>6082</v>
       </c>
       <c r="E6" t="n">
-        <v>19652</v>
+        <v>18679</v>
       </c>
       <c r="F6" t="n">
-        <v>24241</v>
+        <v>12677</v>
       </c>
       <c r="G6" t="n">
-        <v>119566</v>
+        <v>43420</v>
       </c>
       <c r="H6" t="n">
-        <v>8007</v>
+        <v>7785</v>
       </c>
       <c r="I6" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12866</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>10669</v>
+        <v>5341</v>
       </c>
       <c r="AA6" t="n">
-        <v>21709</v>
+        <v>10859</v>
       </c>
       <c r="AB6" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AC6" t="n">
-        <v>13942</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1269,16 +1269,16 @@
         <v>761</v>
       </c>
       <c r="F7" t="n">
-        <v>29513</v>
+        <v>29512</v>
       </c>
       <c r="G7" t="n">
-        <v>9872</v>
+        <v>9754</v>
       </c>
       <c r="H7" t="n">
-        <v>965643</v>
+        <v>457030</v>
       </c>
       <c r="I7" t="n">
-        <v>11940</v>
+        <v>11887</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1621</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>59181</v>
+        <v>29609</v>
       </c>
       <c r="AB7" t="n">
-        <v>15125</v>
+        <v>7569</v>
       </c>
       <c r="AC7" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -1343,16 +1343,16 @@
         <v>90</v>
       </c>
       <c r="F8" t="n">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="G8" t="n">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="H8" t="n">
-        <v>15314</v>
+        <v>14796</v>
       </c>
       <c r="I8" t="n">
-        <v>370494</v>
+        <v>177776</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
